--- a/sources/table_normalization/xlsx/environment-table24.xlsx
+++ b/sources/table_normalization/xlsx/environment-table24.xlsx
@@ -459,12 +459,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -494,6 +492,8 @@
       <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -800,7 +800,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1532,44 +1532,44 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="37" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="36" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="2" customFormat="1" ht="26.15" customHeight="1">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="47" t="s">
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="48" t="s">
+      <c r="L4" s="46" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="91.5" customHeight="1">
-      <c r="A5" s="39"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1597,10 +1597,10 @@
       <c r="J5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="49" t="s">
+      <c r="K5" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="50"/>
+      <c r="L5" s="48"/>
     </row>
     <row r="6" spans="1:13" s="8" customFormat="1" ht="33" customHeight="1">
       <c r="A6" s="5" t="s">
@@ -2263,7 +2263,7 @@
       <c r="O23" s="24"/>
     </row>
     <row r="24" spans="1:15" ht="45" customHeight="1">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="41" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="25">
@@ -2312,7 +2312,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="30" customHeight="1">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="42" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="26">
@@ -2361,7 +2361,7 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="30" customHeight="1">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="42" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="27">
@@ -2410,7 +2410,7 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="30" customHeight="1">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="42" t="s">
         <v>39</v>
       </c>
       <c r="B27" s="29">
@@ -2459,7 +2459,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="30" customHeight="1">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B28" s="31">
@@ -2500,7 +2500,7 @@
       <c r="K29" s="32"/>
     </row>
     <row r="30" spans="1:15" ht="17.5">
-      <c r="A30" s="46" t="s">
+      <c r="A30" s="44" t="s">
         <v>41</v>
       </c>
       <c r="K30" s="33"/>
